--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CUFH reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B769B9-387F-4B2F-B851-8289057B9217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23F2C5A-3D4D-494E-949B-367132E94059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="4425" yWindow="1095" windowWidth="21600" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -616,7 +616,7 @@
         <v>16</v>
       </c>
       <c r="L2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M2">
         <v>17</v>
@@ -669,7 +669,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="M3">
         <v>16</v>

--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23F2C5A-3D4D-494E-949B-367132E94059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ADC2A7-57A1-4418-97D3-0448A8C18BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="1095" windowWidth="21600" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="12015" yWindow="1695" windowWidth="13725" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,10 +129,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -173,17 +174,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -601,7 +605,7 @@
         <v>140</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1">
         <v>14544</v>
@@ -654,7 +658,7 @@
         <v>142</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1">
         <v>12960</v>
@@ -691,51 +695,163 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
+      <c r="B4" s="3">
+        <v>1743</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>517</v>
+      </c>
+      <c r="E4">
+        <v>124</v>
+      </c>
+      <c r="F4">
+        <v>393</v>
+      </c>
+      <c r="G4">
+        <v>39</v>
+      </c>
+      <c r="H4" s="3">
+        <v>20592</v>
+      </c>
+      <c r="I4">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <v>14</v>
+      </c>
+      <c r="K4">
+        <v>31</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>27</v>
+      </c>
+      <c r="N4">
+        <v>6</v>
+      </c>
+      <c r="O4">
+        <v>216</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.95099999999999996</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
+      <c r="B5" s="3">
+        <v>1591</v>
+      </c>
+      <c r="C5">
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <v>602</v>
+      </c>
+      <c r="E5">
+        <v>211</v>
+      </c>
+      <c r="F5">
+        <v>391</v>
+      </c>
+      <c r="G5">
+        <v>29</v>
+      </c>
+      <c r="H5" s="3">
+        <v>17856</v>
+      </c>
+      <c r="I5">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>37</v>
+      </c>
+      <c r="L5">
+        <v>22</v>
+      </c>
+      <c r="M5">
+        <v>30</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>298</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.95699999999999996</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
+      <c r="B6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
+      <c r="B7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
+      <c r="B8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
+      <c r="B9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
+      <c r="B10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
+      <c r="B11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
+      <c r="B12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
+      <c r="B13" s="3"/>
+      <c r="H13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ADC2A7-57A1-4418-97D3-0448A8C18BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E53B8B-BA50-4DA5-8346-1BCAAAC935A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12015" yWindow="1695" windowWidth="13725" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="13050" yWindow="2730" windowWidth="13725" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -791,7 +791,7 @@
         <v>298</v>
       </c>
       <c r="P5" s="2">
-        <v>0.91200000000000003</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="Q5" s="2">
         <v>0.95699999999999996</v>

--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E53B8B-BA50-4DA5-8346-1BCAAAC935A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F48402-6BB8-419C-A4DB-A7B871AE678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="2730" windowWidth="13725" windowHeight="11295" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="12645" yWindow="8025" windowWidth="13725" windowHeight="7215" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
         <v>16</v>
       </c>
       <c r="L2">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="M2">
         <v>17</v>
@@ -673,7 +673,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <v>16</v>

--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F48402-6BB8-419C-A4DB-A7B871AE678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458C4045-E0B6-4835-9D88-5E3C9B33A34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12645" yWindow="8025" windowWidth="13725" windowHeight="7215" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -801,8 +801,54 @@
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="B6" s="3">
+        <v>1380</v>
+      </c>
+      <c r="C6">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>384</v>
+      </c>
+      <c r="E6">
+        <v>166</v>
+      </c>
+      <c r="F6">
+        <v>218</v>
+      </c>
+      <c r="G6">
+        <v>37</v>
+      </c>
+      <c r="H6" s="3">
+        <v>18576</v>
+      </c>
+      <c r="I6">
+        <v>39</v>
+      </c>
+      <c r="J6">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>18</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>356</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.95599999999999996</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">

--- a/facility_data_2026.xlsx
+++ b/facility_data_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AHF\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458C4045-E0B6-4835-9D88-5E3C9B33A34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90FAE36-B67C-4128-A94F-4DDB3A32C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
+    <workbookView xWindow="10140" yWindow="600" windowWidth="17055" windowHeight="12780" xr2:uid="{FF4CAB09-7E04-4EC4-91FD-EE411994FF68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -658,7 +658,7 @@
         <v>142</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1">
         <v>12960</v>
@@ -764,7 +764,7 @@
         <v>391</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H5" s="3">
         <v>17856</v>
@@ -854,15 +854,107 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="B7" s="3">
+        <v>1767</v>
+      </c>
+      <c r="C7">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>645</v>
+      </c>
+      <c r="E7">
+        <v>168</v>
+      </c>
+      <c r="F7">
+        <v>497</v>
+      </c>
+      <c r="G7">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3">
+        <v>12816</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>14</v>
+      </c>
+      <c r="K7">
+        <v>39</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>48</v>
+      </c>
+      <c r="N7">
+        <v>6</v>
+      </c>
+      <c r="O7">
+        <v>385</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.95499999999999996</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="3">
+        <v>1690</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>483</v>
+      </c>
+      <c r="E8">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>379</v>
+      </c>
+      <c r="G8">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3">
+        <v>18864</v>
+      </c>
+      <c r="I8">
+        <v>33</v>
+      </c>
+      <c r="J8">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>27</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>38</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>402</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.91799999999999993</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.95700000000000007</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
